--- a/research/runs/20260228-180047-excel-compat-empirical-pass-01/fixtures/reason_code_wave1.xlsx
+++ b/research/runs/20260228-180047-excel-compat-empirical-pass-01/fixtures/reason_code_wave1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\DnaCalc\Foundation\research\runs\20260228-180047-excel-compat-empirical-pass-01\fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AC3A570-2F6D-40A2-AC96-E18AB732CD5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28087535-5B3F-4341-AF07-12D21FD61598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7440" yWindow="3075" windowWidth="17460" windowHeight="11595" xr2:uid="{3715B3A2-1A1F-4BD3-8F2E-B41F3BFF8CE8}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -71,7 +71,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -414,14 +414,15 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1">
-        <v>1</v>
+        <f ca="1">NOW()</f>
+        <v>46082.014301736112</v>
       </c>
       <c r="B1">
         <v>10</v>
       </c>
       <c r="C1">
-        <f>SUMIF(A1:A3,"&gt;1",B1:B3)</f>
-        <v>50</v>
+        <f ca="1">SUMIF(A1:A3,"&gt;1",B1:B3)</f>
+        <v>60</v>
       </c>
       <c r="D1">
         <v>999</v>
@@ -463,8 +464,8 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
-        <f>_xlfn.VALUETOTEXT(A1)</f>
-        <v>1</v>
+        <f ca="1">_xlfn.VALUETOTEXT(A1)</f>
+        <v>46082.0143017361</v>
       </c>
       <c r="C5" t="str">
         <f>ADDRESS(2,3)</f>
@@ -479,8 +480,8 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C7">
-        <f>INDEX(A1:B2,1,1)</f>
-        <v>1</v>
+        <f ca="1">INDEX(A1:B2,1,1)</f>
+        <v>46082.014301736112</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -503,8 +504,8 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C11">
-        <f>SUMIF(A1:A2,"&gt;15",B1:B2)</f>
-        <v>0</v>
+        <f ca="1">SUMIF(A1:A2,"&gt;15",B1:B2)</f>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
